--- a/新数据生成/关卡表/10010.xlsx
+++ b/新数据生成/关卡表/10010.xlsx
@@ -713,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>24.8</v>
+        <v>19.9</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-4.4</v>
+        <v>-8.5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>粉蝾螈</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>1</v>
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2008</v>
+        <v>2037</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1</v>
@@ -772,14 +772,14 @@
         <v>1.1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>24.8</v>
+        <v>19.9</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-4.4</v>
+        <v>-8.5</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>绿蝙蝠</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>1</v>
@@ -802,27 +802,27 @@
         <v>2004</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>24.8</v>
+        <v>19.9</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-4.4</v>
+        <v>-8.5</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>1</v>
@@ -842,30 +842,30 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2002</v>
+        <v>2031</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>20.3</v>
+        <v>17.5</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英黄石怪</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>1</v>
@@ -885,30 +885,30 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2007</v>
+        <v>2044</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>20.3</v>
+        <v>17.5</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>垃圾刺客</t>
+          <t>精英绿花</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>1</v>
@@ -927,25 +927,41 @@
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="n">
+        <v>2043</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" s="2" t="n">
-        <v>20.3</v>
+        <v>17.5</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+        <v>2.3</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>精英绿蝙蝠</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="n">
+        <v>3.2</v>
+      </c>
       <c r="P12" s="2" t="n">
         <v>1</v>
       </c>
@@ -955,39 +971,39 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="F13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>16.4</v>
+        <v>13.4</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-2.2</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>黄蝾螈</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>1</v>
@@ -998,7 +1014,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>12</v>
@@ -1008,29 +1024,29 @@
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>16.4</v>
+        <v>13.4</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-2.2</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>1</v>
@@ -1047,15 +1063,15 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="n">
-        <v>16.4</v>
+        <v>13.4</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-2.2</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
@@ -1068,30 +1084,30 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>13.7</v>
+        <v>8.4</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄电兔</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1100,7 +1116,7 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>1</v>
@@ -1111,30 +1127,30 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="F17" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="G17" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>2</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>13.7</v>
+        <v>8.4</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-0.9</v>
+        <v>-0.4</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1143,7 +1159,7 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P17" s="2" t="n">
         <v>1</v>
@@ -1153,41 +1169,25 @@
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>2</v>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="n">
-        <v>13.7</v>
+        <v>8.4</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>-0.4</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>3.1</v>
-      </c>
+      <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="n">
         <v>1</v>
       </c>
@@ -1197,13 +1197,13 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2003</v>
+        <v>2024</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
@@ -1213,14 +1213,14 @@
         <v>1.1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>21.4</v>
+        <v>18.6</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-7.6</v>
+        <v>-9.1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄蝾螈</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>1</v>
@@ -1240,13 +1240,13 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
@@ -1256,14 +1256,14 @@
         <v>1</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>21.4</v>
+        <v>18.6</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-7.6</v>
+        <v>-9.1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>1</v>
@@ -1282,41 +1282,25 @@
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="n">
-        <v>21.4</v>
+        <v>18.6</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>-9.1</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>3.1</v>
-      </c>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="n">
         <v>1</v>
       </c>
@@ -1326,30 +1310,30 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>-1.3</v>
+        <v>-3.2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>黄鹿角</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1358,7 +1342,7 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>1</v>
@@ -1369,30 +1353,30 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>-1.3</v>
+        <v>-3.2</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -1401,7 +1385,7 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P23" s="2" t="n">
         <v>1</v>
@@ -1418,10 +1402,10 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>-1.3</v>
+        <v>-3.2</v>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
@@ -1439,30 +1423,30 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-6.6</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>粉蝙蝠</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -1471,7 +1455,7 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P25" s="2" t="n">
         <v>1</v>
@@ -1482,30 +1466,30 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2004</v>
+        <v>2038</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-6.6</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -1514,7 +1498,7 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P26" s="2" t="n">
         <v>1</v>
@@ -1524,25 +1508,41 @@
       <c r="D27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K27" s="2" t="n">
-        <v>14.9</v>
+        <v>12.2</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+        <v>-6.6</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>紫蝙蝠</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="n">
+        <v>3.2</v>
+      </c>
       <c r="P27" s="2" t="n">
         <v>1</v>
       </c>
@@ -1552,30 +1552,30 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2004</v>
+        <v>2039</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>11.2</v>
+        <v>13.9</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>-2.4</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿螃蟹</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P28" s="2" t="n">
         <v>1</v>
@@ -1595,30 +1595,30 @@
         <v>8</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>11.2</v>
+        <v>13.9</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>-2.4</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P29" s="2" t="n">
         <v>1</v>
@@ -1637,41 +1637,25 @@
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="n">
-        <v>11.2</v>
+        <v>13.9</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O30" s="2" t="n">
-        <v>3.1</v>
-      </c>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="n">
         <v>1</v>
       </c>
@@ -1681,39 +1665,39 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2003</v>
+        <v>2037</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>26.6</v>
+        <v>12.2</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-6.7</v>
+        <v>-2.1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿蝙蝠</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P31" s="2" t="n">
         <v>1</v>
@@ -1724,39 +1708,39 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>26.6</v>
+        <v>12.2</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>-6.7</v>
+        <v>-2.1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄树怪</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P32" s="2" t="n">
         <v>1</v>
@@ -1766,41 +1750,25 @@
       <c r="D33" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="n">
-        <v>26.6</v>
+        <v>12.2</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>-2.1</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>3.1</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="n">
         <v>1</v>
       </c>
@@ -1813,36 +1781,36 @@
         <v>2001</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>-3.7</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>黄鹿角</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P34" s="2" t="n">
         <v>1</v>
@@ -1853,39 +1821,39 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2004</v>
+        <v>2026</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>-3.7</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P35" s="2" t="n">
         <v>1</v>
@@ -1902,15 +1870,15 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>23.7</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>-3.7</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
@@ -1923,39 +1891,39 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2003</v>
+        <v>2036</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>19.7</v>
+        <v>12.9</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-9.4</v>
+        <v>3.5</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿兔子</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P37" s="2" t="n">
         <v>1</v>
@@ -1966,39 +1934,39 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2004</v>
+        <v>2027</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>19.7</v>
+        <v>12.9</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>-9.4</v>
+        <v>3.5</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P38" s="2" t="n">
         <v>1</v>
@@ -2008,41 +1976,25 @@
       <c r="D39" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="n">
-        <v>19.7</v>
+        <v>12.9</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>-9.4</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="n">
-        <v>3.1</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="n">
         <v>1</v>
       </c>
@@ -2052,39 +2004,39 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2008</v>
+        <v>2023</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>16.6</v>
+        <v>10.7</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>-9.1</v>
+        <v>1.1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>粉蝾螈</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P40" s="2" t="n">
         <v>1</v>
@@ -2095,39 +2047,39 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2004</v>
+        <v>2038</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>16.6</v>
+        <v>10.7</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>-9.1</v>
+        <v>1.1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P41" s="2" t="n">
         <v>1</v>
@@ -2138,39 +2090,39 @@
         <v>12</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2003</v>
+        <v>2037</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>16.6</v>
+        <v>10.7</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>-9.1</v>
+        <v>1.1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿蝙蝠</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P42" s="2" t="n">
         <v>1</v>
@@ -2181,30 +2133,30 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2003</v>
+        <v>2038</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>20</v>
+        <v>24.8</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-4.1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2213,7 +2165,7 @@
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P43" s="2" t="n">
         <v>1</v>
@@ -2224,30 +2176,30 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2004</v>
+        <v>2024</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>20</v>
+        <v>24.8</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>-4.1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄蝾螈</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2256,7 +2208,7 @@
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P44" s="2" t="n">
         <v>1</v>
@@ -2267,30 +2219,30 @@
         <v>13</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="F45" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G45" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>3</v>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>20</v>
+        <v>24.8</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>-4.1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>黄鹿角</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2299,7 +2251,7 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P45" s="2" t="n">
         <v>1</v>
@@ -2310,39 +2262,39 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2004</v>
+        <v>2040</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>28</v>
+        <v>10.7</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>-8.199999999999999</v>
+        <v>-2.2</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P46" s="2" t="n">
         <v>1</v>
@@ -2353,39 +2305,39 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>28</v>
+        <v>10.7</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>-8.199999999999999</v>
+        <v>-2.2</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿皮怪1</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P47" s="2" t="n">
         <v>1</v>
@@ -2395,41 +2347,25 @@
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="n">
-        <v>28</v>
+        <v>10.7</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>-2.2</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>3.1</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="n">
         <v>1</v>
       </c>
@@ -2439,30 +2375,30 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>15.6</v>
+        <v>18</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>岩石龟</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -2471,7 +2407,7 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P49" s="2" t="n">
         <v>1</v>
@@ -2482,30 +2418,30 @@
         <v>15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>15.6</v>
+        <v>18</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>紫蝙蝠</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -2514,7 +2450,7 @@
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P50" s="2" t="n">
         <v>1</v>
@@ -2525,32 +2461,30 @@
         <v>15</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>3004</v>
+        <v>2007</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>786</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>15.6</v>
+        <v>18</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -2559,7 +2493,7 @@
         </is>
       </c>
       <c r="O51" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P51" s="2" t="n">
         <v>1</v>
@@ -2570,30 +2504,30 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>13.9</v>
+        <v>25.6</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>-4.6</v>
+        <v>-5</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄树怪</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -2602,7 +2536,7 @@
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P52" s="2" t="n">
         <v>1</v>
@@ -2613,30 +2547,30 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>13.9</v>
+        <v>25.6</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>-4.6</v>
+        <v>-5</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -2645,7 +2579,7 @@
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P53" s="2" t="n">
         <v>1</v>
@@ -2662,10 +2596,10 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="n">
-        <v>13.9</v>
+        <v>25.6</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>-4.6</v>
+        <v>-5</v>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
@@ -2683,30 +2617,30 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2003</v>
+        <v>2035</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>-4.6</v>
+        <v>-8.5</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>绿蝾螈</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -2715,7 +2649,7 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P55" s="2" t="n">
         <v>1</v>
@@ -2726,13 +2660,13 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
@@ -2742,14 +2676,14 @@
         <v>1.2</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>-4.6</v>
+        <v>-8.5</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -2758,7 +2692,7 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P56" s="2" t="n">
         <v>1</v>
@@ -2775,10 +2709,10 @@
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="n">
-        <v>16.2</v>
+        <v>15.6</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>-4.6</v>
+        <v>-8.5</v>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
@@ -2796,39 +2730,39 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>18.5</v>
+        <v>12.4</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>-3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>蜗牛</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P58" s="2" t="n">
         <v>1</v>
@@ -2839,39 +2773,39 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2003</v>
+        <v>2028</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>18.5</v>
+        <v>12.4</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>-3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P59" s="2" t="n">
         <v>1</v>
@@ -2881,41 +2815,25 @@
       <c r="D60" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="n">
-        <v>18.5</v>
+        <v>12.4</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>3.1</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="n">
         <v>1</v>
       </c>
@@ -2925,30 +2843,30 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>22.3</v>
+        <v>25.8</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>-4.3</v>
+        <v>-5.7</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄鹿角</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -2957,7 +2875,7 @@
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P61" s="2" t="n">
         <v>1</v>
@@ -2968,30 +2886,30 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2003</v>
+        <v>2024</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>22.3</v>
+        <v>25.8</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>-4.3</v>
+        <v>-5.7</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>黄蝾螈</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -3000,7 +2918,7 @@
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P62" s="2" t="n">
         <v>1</v>
@@ -3017,10 +2935,10 @@
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="n">
-        <v>22.3</v>
+        <v>25.8</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>-4.3</v>
+        <v>-5.7</v>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
@@ -3038,39 +2956,39 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2008</v>
+        <v>2025</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>-5</v>
+        <v>1.9</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P64" s="2" t="n">
         <v>1</v>
@@ -3081,39 +2999,39 @@
         <v>20</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2003</v>
+        <v>2023</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>-5</v>
+        <v>1.9</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>粉蝾螈</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P65" s="2" t="n">
         <v>1</v>
@@ -3124,39 +3042,39 @@
         <v>20</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>2004</v>
+        <v>2028</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>-5</v>
+        <v>1.9</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>黄犀牛</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O66" s="2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P66" s="2" t="n">
         <v>1</v>

--- a/新数据生成/关卡表/10010.xlsx
+++ b/新数据生成/关卡表/10010.xlsx
@@ -713,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2023</v>
+        <v>2040</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>6</v>
@@ -723,20 +723,20 @@
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>19.9</v>
+        <v>18.4</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-8.5</v>
+        <v>-8.9</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>粉蝾螈</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>6</v>
@@ -769,17 +769,15 @@
         <v>0.7</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>19.9</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="n">
-        <v>-8.5</v>
+        <v>-8.9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>绿蝙蝠</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -799,30 +797,28 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2004</v>
+        <v>2027</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="n">
-        <v>-8.5</v>
+        <v>-8.9</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -842,30 +838,30 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>精英黄石怪</t>
+          <t>精英黄犀牛</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -885,30 +881,28 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2044</v>
+        <v>2029</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
         <v>0.8</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>17.5</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="n">
-        <v>2.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>精英绿花</t>
+          <t>精英粉蝾螈</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -927,41 +921,23 @@
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>2043</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>17.5</v>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>精英绿蝙蝠</t>
-        </is>
-      </c>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>3.2</v>
-      </c>
+      <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="n">
         <v>1</v>
       </c>
@@ -971,35 +947,35 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>13.4</v>
+        <v>12.9</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-8.699999999999999</v>
+        <v>-1.8</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>黄蝾螈</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
@@ -1014,35 +990,33 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2007</v>
+        <v>2038</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>13.4</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="n">
-        <v>-8.699999999999999</v>
+        <v>-1.8</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
@@ -1062,16 +1036,14 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="n">
-        <v>13.4</v>
-      </c>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="n">
-        <v>-8.699999999999999</v>
+        <v>-1.8</v>
       </c>
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr"/>
@@ -1084,35 +1056,35 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2002</v>
+        <v>2038</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-0.4</v>
+        <v>-6.6</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>黄电兔</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
@@ -1127,35 +1099,33 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2006</v>
+        <v>2040</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>8.4</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="n">
-        <v>-0.4</v>
+        <v>-6.6</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O17" s="2" t="n">
@@ -1175,16 +1145,14 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="n">
-        <v>-0.4</v>
+        <v>-6.6</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
@@ -1197,35 +1165,35 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>18.6</v>
+        <v>14.8</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-9.1</v>
+        <v>-1.9</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>黄蝾螈</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O19" s="2" t="n">
@@ -1240,35 +1208,33 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2007</v>
+        <v>2038</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>18.6</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="n">
-        <v>-9.1</v>
+        <v>-1.9</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
@@ -1288,16 +1254,14 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="n">
-        <v>-9.1</v>
+        <v>-1.9</v>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
@@ -1310,35 +1274,35 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2001</v>
+        <v>2040</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>9.4</v>
+        <v>25.5</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>-3.2</v>
+        <v>-7.7</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>黄鹿角</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O22" s="2" t="n">
@@ -1353,35 +1317,33 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2006</v>
+        <v>2038</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" s="2" t="n">
-        <v>9.4</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="n">
-        <v>-3.2</v>
+        <v>-7.7</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O23" s="2" t="n">
@@ -1395,25 +1357,39 @@
       <c r="D24" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="n">
-        <v>9.4</v>
-      </c>
+      <c r="I24" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+        <v>-7.7</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>黄战士</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>3.2</v>
+      </c>
       <c r="P24" s="2" t="n">
         <v>1</v>
       </c>
@@ -1423,35 +1399,35 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2004</v>
+        <v>2025</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>12.2</v>
+        <v>13.4</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-6.6</v>
+        <v>-3.3</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>粉蝙蝠</t>
+          <t>黄石怪</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
@@ -1469,23 +1445,21 @@
         <v>2038</v>
       </c>
       <c r="F26" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>12.2</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="n">
-        <v>-6.6</v>
+        <v>-3.3</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -1494,7 +1468,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O26" s="2" t="n">
@@ -1508,41 +1482,23 @@
       <c r="D27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>紫蝙蝠</t>
-        </is>
-      </c>
+        <v>-3.3</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="n">
-        <v>3.2</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="n">
         <v>1</v>
       </c>
@@ -1552,35 +1508,35 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>-5.7</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>绿螃蟹</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O28" s="2" t="n">
@@ -1595,35 +1551,33 @@
         <v>8</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2007</v>
+        <v>2038</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K29" s="2" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>-5.7</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O29" s="2" t="n">
@@ -1643,16 +1597,14 @@
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="2" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>-5.7</v>
       </c>
       <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr"/>
@@ -1665,10 +1617,10 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>7</v>
@@ -1678,17 +1630,17 @@
         <v>1.1</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>12.2</v>
+        <v>9.9</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>绿蝙蝠</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -1708,10 +1660,10 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2003</v>
+        <v>2027</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>7</v>
@@ -1723,15 +1675,13 @@
       <c r="J32" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K32" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="n">
-        <v>-2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>黄树怪</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -1756,11 +1706,9 @@
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="n">
-        <v>12.2</v>
-      </c>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="n">
-        <v>-2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
@@ -1778,10 +1726,10 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2001</v>
+        <v>2038</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>7</v>
@@ -1794,14 +1742,14 @@
         <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>23.7</v>
+        <v>21.4</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>-8.800000000000001</v>
+        <v>-4.2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>黄鹿角</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -1821,10 +1769,10 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>7</v>
@@ -1834,17 +1782,15 @@
         <v>0.6</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>23.7</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="n">
-        <v>-8.800000000000001</v>
+        <v>-4.2</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -1869,11 +1815,9 @@
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="2" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="n">
-        <v>-8.800000000000001</v>
+        <v>-4.2</v>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
@@ -1891,30 +1835,30 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2036</v>
+        <v>2027</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>3.5</v>
+        <v>-0.7</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>绿兔子</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -1934,10 +1878,10 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2027</v>
+        <v>2040</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>8</v>
@@ -1947,17 +1891,15 @@
         <v>1</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>12.9</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="n">
-        <v>3.5</v>
+        <v>-0.7</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>黄战士</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -1976,25 +1918,39 @@
       <c r="D39" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="n">
-        <v>12.9</v>
-      </c>
+      <c r="I39" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+        <v>-0.7</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>绿花</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="n">
+        <v>3.2</v>
+      </c>
       <c r="P39" s="2" t="n">
         <v>1</v>
       </c>
@@ -2004,35 +1960,35 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2023</v>
+        <v>2040</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>10.7</v>
+        <v>26.3</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1.1</v>
+        <v>-10</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>粉蝾螈</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O40" s="2" t="n">
@@ -2047,35 +2003,33 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2038</v>
+        <v>2027</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K41" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="n">
-        <v>1.1</v>
+        <v>-10</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>绿花</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O41" s="2" t="n">
@@ -2089,41 +2043,23 @@
       <c r="D42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>2037</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>绿蝙蝠</t>
-        </is>
-      </c>
+        <v>-10</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>3.2</v>
-      </c>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="n">
         <v>1</v>
       </c>
@@ -2133,13 +2069,13 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2038</v>
+        <v>2027</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
@@ -2149,14 +2085,14 @@
         <v>1.1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>绿花</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2176,30 +2112,28 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2024</v>
+        <v>2038</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>24.8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>黄蝾螈</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -2219,13 +2153,13 @@
         <v>13</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2001</v>
+        <v>2040</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="n">
@@ -2234,15 +2168,13 @@
       <c r="J45" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K45" s="2" t="n">
-        <v>24.8</v>
-      </c>
+      <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>黄鹿角</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -2265,23 +2197,23 @@
         <v>2040</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>8</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>10.7</v>
+        <v>22.9</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>-2.2</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -2290,7 +2222,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O46" s="2" t="n">
@@ -2305,35 +2237,33 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2006</v>
+        <v>2038</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>10.7</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="n">
-        <v>-2.2</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>绿皮怪1</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O47" s="2" t="n">
@@ -2347,25 +2277,39 @@
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="I48" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>黄战士</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr"/>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>3.2</v>
+      </c>
       <c r="P48" s="2" t="n">
         <v>1</v>
       </c>
@@ -2375,35 +2319,35 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2005</v>
+        <v>2040</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>18</v>
+        <v>21.2</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>5.5</v>
+        <v>-9.9</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>岩石龟</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O49" s="2" t="n">
@@ -2418,35 +2362,33 @@
         <v>15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>18</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="n">
-        <v>5.5</v>
+        <v>-9.9</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>紫蝙蝠</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O50" s="2" t="n">
@@ -2461,35 +2403,33 @@
         <v>15</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2007</v>
+        <v>2038</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>18</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="n">
-        <v>5.5</v>
+        <v>-9.9</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O51" s="2" t="n">
@@ -2504,30 +2444,30 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2003</v>
+        <v>2038</v>
       </c>
       <c r="F52" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G52" s="2" t="n">
         <v>8</v>
-      </c>
-      <c r="G52" s="2" t="n">
-        <v>9</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>25.6</v>
+        <v>21.2</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>-5</v>
+        <v>-8.1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>黄树怪</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -2547,10 +2487,10 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2007</v>
+        <v>2040</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>8</v>
@@ -2560,17 +2500,15 @@
         <v>0.5</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K53" s="2" t="n">
-        <v>25.6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="n">
-        <v>-5</v>
+        <v>-8.1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -2589,25 +2527,39 @@
       <c r="D54" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="n">
-        <v>25.6</v>
-      </c>
+      <c r="I54" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+        <v>-8.1</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>黄战士</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="n">
+        <v>3.2</v>
+      </c>
       <c r="P54" s="2" t="n">
         <v>1</v>
       </c>
@@ -2617,7 +2569,7 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2035</v>
+        <v>2027</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>11</v>
@@ -2630,17 +2582,17 @@
         <v>0.6</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>15.6</v>
+        <v>16.3</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>-8.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>绿蝾螈</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -2660,10 +2612,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2007</v>
+        <v>2038</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>7</v>
@@ -2675,15 +2627,13 @@
       <c r="J56" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="K56" s="2" t="n">
-        <v>15.6</v>
-      </c>
+      <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="n">
-        <v>-8.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -2708,11 +2658,9 @@
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="2" t="n">
-        <v>15.6</v>
-      </c>
+      <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="n">
-        <v>-8.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
@@ -2730,35 +2678,35 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2007</v>
+        <v>2027</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G58" s="2" t="n">
         <v>9</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>12.4</v>
+        <v>22.5</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2.7</v>
+        <v>-6.8</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>蜗牛</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O58" s="2" t="n">
@@ -2773,35 +2721,33 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2028</v>
+        <v>2040</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>9</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J59" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="J59" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="n">
-        <v>2.7</v>
+        <v>-6.8</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>黄犀牛</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O59" s="2" t="n">
@@ -2815,25 +2761,39 @@
       <c r="D60" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="n">
+        <v>2038</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="I60" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+        <v>-6.8</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>绿花</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr"/>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>3.2</v>
+      </c>
       <c r="P60" s="2" t="n">
         <v>1</v>
       </c>
@@ -2843,7 +2803,7 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2001</v>
+        <v>2040</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>7</v>
@@ -2853,20 +2813,20 @@
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>25.8</v>
+        <v>20.7</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>-5.7</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>黄鹿角</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -2886,7 +2846,7 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2024</v>
+        <v>2038</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>6</v>
@@ -2896,20 +2856,18 @@
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K62" s="2" t="n">
-        <v>25.8</v>
-      </c>
+      <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="n">
-        <v>-5.7</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>黄蝾螈</t>
+          <t>绿花</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -2934,11 +2892,9 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="n">
-        <v>25.8</v>
-      </c>
+      <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="n">
-        <v>-5.7</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
@@ -2956,35 +2912,35 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>10.5</v>
+        <v>23.1</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1.9</v>
+        <v>-3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>黄石怪</t>
+          <t>黄战士</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O64" s="2" t="n">
@@ -2999,35 +2955,33 @@
         <v>20</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2023</v>
+        <v>2040</v>
       </c>
       <c r="F65" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G65" s="2" t="n">
         <v>9</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>10</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K65" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="n">
-        <v>1.9</v>
+        <v>-3</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>粉蝾螈</t>
+          <t>绿蘑菇</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O65" s="2" t="n">
@@ -3041,41 +2995,23 @@
       <c r="D66" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K66" s="2" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>黄犀牛</t>
-        </is>
-      </c>
+        <v>-3</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="n">
-        <v>3.2</v>
-      </c>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="n">
         <v>1</v>
       </c>
